--- a/artfynd/A 11217-2024 artfynd.xlsx
+++ b/artfynd/A 11217-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY6"/>
+  <dimension ref="A1:AY7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,15 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>786998</v>
+        <v>7099555</v>
       </c>
       <c r="B2" t="n">
-        <v>93131</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>96554</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -691,34 +686,49 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>2671</v>
+        <v>210</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Fällmossa</t>
+          <t>Grön sköldmossa</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Antitrichia curtipendula</t>
+          <t>Buxbaumia viridis</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Hedw.) Brid.</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr"/>
+          <t>(Moug. ex Lam. &amp; DC.) Brid. ex Moug. &amp; Nestl.</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>kapslar</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>med kapsel</t>
+        </is>
+      </c>
+      <c r="L2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Jälla, ca 900m NNO, Upl</t>
+          <t>Sjödyn, 0,8 km S-ut, Upl</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>652104.0902335554</v>
+        <v>652141</v>
       </c>
       <c r="R2" t="n">
-        <v>6644966.141177366</v>
+        <v>6644980</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -745,22 +755,12 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2010-08-29</t>
-        </is>
-      </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2013-07-11</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2010-08-29</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2013-07-11</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -772,43 +772,54 @@
       <c r="AG2" t="b">
         <v>0</v>
       </c>
-      <c r="AI2" t="inlineStr">
-        <is>
-          <t>Blandskog</t>
-        </is>
-      </c>
-      <c r="AN2" t="n">
-        <v>1</v>
+      <c r="AH2" t="inlineStr">
+        <is>
+          <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AJ2" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK2" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM2" t="inlineStr">
+        <is>
+          <t>Stubbe</t>
+        </is>
       </c>
       <c r="AO2" t="inlineStr">
         <is>
-          <t>1 substratenheter</t>
+          <t>Stump # Stubbe # Picea abies</t>
         </is>
       </c>
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Mattias Lif</t>
+          <t>Henry Åkerström</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Mattias Lif</t>
-        </is>
-      </c>
-      <c r="AY2" t="inlineStr"/>
+          <t>Thorleif Joelson, Henry Åkerström</t>
+        </is>
+      </c>
+      <c r="AY2" t="inlineStr">
+        <is>
+          <t>Naturskyddsföreningen Uppsala, skogsgruppexkursion</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>2132193</v>
+        <v>76112476</v>
       </c>
       <c r="B3" t="n">
-        <v>77881</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91920</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -816,34 +827,34 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6431</v>
+        <v>1205</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Lönnlav</t>
+          <t>Stor aspticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Bacidia rubella</t>
+          <t>Phellinus populicola</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Hoffm.) A.Massal.</t>
+          <t>Niemelä</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Jälla, ca 900m NNO, Upl</t>
+          <t>Jälla, Upl</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>652150.8113071473</v>
+        <v>652149</v>
       </c>
       <c r="R3" t="n">
-        <v>6644979.610104551</v>
+        <v>6644922</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -870,22 +881,17 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2010-08-29</t>
-        </is>
-      </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2018-08-01</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2010-08-29</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2018-10-31</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>Fynden gjordes mellan augusti och oktober 2018.</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -896,44 +902,26 @@
       </c>
       <c r="AG3" t="b">
         <v>0</v>
-      </c>
-      <c r="AI3" t="inlineStr">
-        <is>
-          <t>Blandskog</t>
-        </is>
-      </c>
-      <c r="AN3" t="n">
-        <v>1</v>
-      </c>
-      <c r="AO3" t="inlineStr">
-        <is>
-          <t>1 substratenheter</t>
-        </is>
       </c>
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Mattias Lif</t>
+          <t>Magnus Stenmark</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Mattias Lif</t>
+          <t>Sofia Lundell, Karin Agstam-Norlin</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>7099555</v>
+        <v>76112477</v>
       </c>
       <c r="B4" t="n">
-        <v>93235</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91920</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -941,49 +929,34 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>210</v>
+        <v>1205</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Grön sköldmossa</t>
+          <t>Stor aspticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Buxbaumia viridis</t>
+          <t>Phellinus populicola</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Moug. ex Lam. &amp; DC.) Brid. ex Moug. &amp; Nestl.</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t>kapslar</t>
-        </is>
-      </c>
-      <c r="K4" t="inlineStr">
-        <is>
-          <t>med kapsel</t>
-        </is>
-      </c>
-      <c r="L4" t="inlineStr"/>
+          <t>Niemelä</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Sjödyn, 0,8 km S-ut, Upl</t>
+          <t>Jälla, Upl</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>652140.7491955019</v>
+        <v>652160</v>
       </c>
       <c r="R4" t="n">
-        <v>6644979.698363874</v>
+        <v>6644921</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1010,22 +983,17 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2013-07-11</t>
-        </is>
-      </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2018-08-01</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2013-07-11</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2018-10-31</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>Fynden gjordes mellan augusti och oktober 2018.</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1036,60 +1004,26 @@
       </c>
       <c r="AG4" t="b">
         <v>0</v>
-      </c>
-      <c r="AH4" t="inlineStr">
-        <is>
-          <t>Barrskog</t>
-        </is>
-      </c>
-      <c r="AJ4" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK4" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM4" t="inlineStr">
-        <is>
-          <t>Stubbe</t>
-        </is>
-      </c>
-      <c r="AO4" t="inlineStr">
-        <is>
-          <t>Stump # Stubbe # Picea abies</t>
-        </is>
       </c>
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Henry Åkerström</t>
+          <t>Magnus Stenmark</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Henry Åkerström, Thorleif Joelson</t>
-        </is>
-      </c>
-      <c r="AY4" t="inlineStr">
-        <is>
-          <t>Naturskyddsföreningen Uppsala, skogsgruppexkursion</t>
-        </is>
-      </c>
+          <t>Sofia Lundell, Karin Agstam-Norlin</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>76112477</v>
+        <v>786998</v>
       </c>
       <c r="B5" t="n">
-        <v>89403</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>96426</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1097,34 +1031,34 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>1205</v>
+        <v>2671</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Stor aspticka</t>
+          <t>Fällmossa</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Phellinus populicola</t>
+          <t>Antitrichia curtipendula</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>Niemelä</t>
+          <t>(Hedw.) Brid.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Jälla, Upl</t>
+          <t>Jälla, ca 900m NNO, Upl</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>652159.7502475174</v>
+        <v>652104</v>
       </c>
       <c r="R5" t="n">
-        <v>6644921.23464046</v>
+        <v>6644966</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1151,27 +1085,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2018-08-01</t>
-        </is>
-      </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2010-08-29</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2018-10-31</t>
-        </is>
-      </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="AC5" t="inlineStr">
-        <is>
-          <t>Fynden gjordes mellan augusti och oktober 2018.</t>
+          <t>2010-08-29</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1182,31 +1101,39 @@
       </c>
       <c r="AG5" t="b">
         <v>0</v>
+      </c>
+      <c r="AI5" t="inlineStr">
+        <is>
+          <t>Blandskog</t>
+        </is>
+      </c>
+      <c r="AN5" t="n">
+        <v>1</v>
+      </c>
+      <c r="AO5" t="inlineStr">
+        <is>
+          <t>1 substratenheter</t>
+        </is>
       </c>
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Magnus Stenmark</t>
+          <t>Mattias Lif</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Sofia Lundell, Karin Agstam-Norlin</t>
+          <t>Mattias Lif</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>76112476</v>
+        <v>7099556</v>
       </c>
       <c r="B6" t="n">
-        <v>89403</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>96426</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1214,34 +1141,37 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>1205</v>
+        <v>2671</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Stor aspticka</t>
+          <t>Fällmossa</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Phellinus populicola</t>
+          <t>Antitrichia curtipendula</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>Niemelä</t>
+          <t>(Hedw.) Brid.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
+      <c r="J6" t="inlineStr"/>
+      <c r="K6" t="inlineStr"/>
+      <c r="L6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Jälla, Upl</t>
+          <t>Sjödyn, 0,8 km S-ut, Upl</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>652149.1652793479</v>
+        <v>652155</v>
       </c>
       <c r="R6" t="n">
-        <v>6644921.803470757</v>
+        <v>6645023</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1268,27 +1198,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2018-08-01</t>
-        </is>
-      </c>
-      <c r="Z6" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2013-07-11</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2018-10-31</t>
-        </is>
-      </c>
-      <c r="AB6" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="AC6" t="inlineStr">
-        <is>
-          <t>Fynden gjordes mellan augusti och oktober 2018.</t>
+          <t>2013-07-11</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1299,19 +1214,143 @@
       </c>
       <c r="AG6" t="b">
         <v>0</v>
+      </c>
+      <c r="AH6" t="inlineStr">
+        <is>
+          <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AO6" t="inlineStr">
+        <is>
+          <t>Stenblock</t>
+        </is>
       </c>
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Magnus Stenmark</t>
+          <t>Henry Åkerström</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Sofia Lundell, Karin Agstam-Norlin</t>
-        </is>
-      </c>
-      <c r="AY6" t="inlineStr"/>
+          <t>Thorleif Joelson, Henry Åkerström</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr">
+        <is>
+          <t>Naturskyddsföreningen Uppsala, skogsgruppexkursion</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>2132193</v>
+      </c>
+      <c r="B7" t="n">
+        <v>79707</v>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>6431</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Lönnlav</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Bacidia rubella</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>(Hoffm.) A.Massal.</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>Jälla, ca 900m NNO, Upl</t>
+        </is>
+      </c>
+      <c r="Q7" t="n">
+        <v>652151</v>
+      </c>
+      <c r="R7" t="n">
+        <v>6644980</v>
+      </c>
+      <c r="S7" t="n">
+        <v>10</v>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>Vaksala</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>2010-08-29</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>2010-08-29</t>
+        </is>
+      </c>
+      <c r="AD7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI7" t="inlineStr">
+        <is>
+          <t>Blandskog</t>
+        </is>
+      </c>
+      <c r="AN7" t="n">
+        <v>1</v>
+      </c>
+      <c r="AO7" t="inlineStr">
+        <is>
+          <t>1 substratenheter</t>
+        </is>
+      </c>
+      <c r="AT7" t="inlineStr"/>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>Mattias Lif</t>
+        </is>
+      </c>
+      <c r="AX7" t="inlineStr">
+        <is>
+          <t>Mattias Lif</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
